--- a/PANDA_Reproducibility/supporting_information/S1_Table.xlsx
+++ b/PANDA_Reproducibility/supporting_information/S1_Table.xlsx
@@ -836,7 +836,11 @@
       <c r="H12" t="n">
         <v>111370</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Fig 11</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">

--- a/PANDA_Reproducibility/supporting_information/S1_Table.xlsx
+++ b/PANDA_Reproducibility/supporting_information/S1_Table.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fig 11</t>
+          <t>Fig 7</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Fig 15B</t>
+          <t>Fig 10B</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Fig 15C</t>
+          <t>Fig 10C</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Fig 14B</t>
+          <t>Fig 9B</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Fig 14C</t>
+          <t>Fig 9C</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Fig 15A</t>
+          <t>Fig 10A</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Fig 14A</t>
+          <t>Fig 9A</t>
         </is>
       </c>
     </row>
